--- a/sampleprojects/TaxReturn/excel/states/NJ.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/NJ.xlsx
@@ -68,7 +68,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.nj_tax = 0; set result.nj_exemption_total = 0; set result.nj_taxable_income = 0; set result.nj_agi = result.agi; set result.nj_exemption_total = length of job.taxpayers * nj_personal_exemption + length of job.dependents * nj_dependent_exemption; set result.nj_taxable_income = the maximum of (result.nj_agi - result.nj_exemption_total) and 0; add "NEW JERSEY FORM NJ-1040 - State Income Tax Calculation" to job.audit_trail</t>
+    <t>set result.nj_tax = 0; set result.nj_exemption_total = 0; set result.nj_taxable_income = 0; set result.nj_agi = result.state_calc_agi; set result.nj_exemption_total = length of job.taxpayers * nj_personal_exemption + length of job.dependents * nj_dependent_exemption; set result.nj_taxable_income = the maximum of (result.nj_agi - result.nj_exemption_total) and 0; add "NEW JERSEY FORM NJ-1040 - State Income Tax Calculation" to job.audit_trail</t>
   </si>
   <si>
     <t>Joint filers use the joint bracket schedule</t>

--- a/sampleprojects/TaxReturn/excel/states/NJ.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/NJ.xlsx
@@ -74,7 +74,7 @@
     <t>Joint filers use the joint bracket schedule</t>
   </si>
   <si>
-    <t>job.filing_status is equal to "married_filing_jointly" OR job.filing_status is equal to "MFJ"</t>
+    <t>job.filing_status is equal to "MFJ"</t>
   </si>
   <si>
     <t>Y</t>
